--- a/examples/excel/charts/charts-histogram.xlsx
+++ b/examples/excel/charts/charts-histogram.xlsx
@@ -3,11 +3,11 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-Hero" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Binning Lab" sheetId="2" r:id="R72a9cd19bdac44d3"/>
-    <x:sheet name="2-Distribution Zoo" sheetId="3" r:id="R49082c18c3474309"/>
-    <x:sheet name="3-Theme Gallery" sheetId="4" r:id="Rd6f10f3a2d084f5e"/>
-    <x:sheet name="4-Typography" sheetId="5" r:id="Rca17bac0bbb14e96"/>
-    <x:sheet name="5-ML Dashboard" sheetId="6" r:id="R63f59425559d472c"/>
+    <x:sheet name="1-Binning Lab" sheetId="2" r:id="R1cb043f761074945"/>
+    <x:sheet name="2-Distribution Zoo" sheetId="3" r:id="R4e9e0281daa1408f"/>
+    <x:sheet name="3-Theme Gallery" sheetId="4" r:id="R9557f557d5da4915"/>
+    <x:sheet name="4-Typography" sheetId="5" r:id="Rf7c8ebe6e83f4ad1"/>
+    <x:sheet name="5-ML Dashboard" sheetId="6" r:id="Rf9ac993909a942b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,7 +38,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R9e96f1d90df14d3c"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf38c7822d7374e57"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -73,7 +73,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3aade38a7b274302"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R2eef917c36c64e90"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -103,7 +103,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rbb3038fcbc8b4290"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Redf8fba7fc744469"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -133,7 +133,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R17f351bb0f5e413e"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rcfd91ac8d1b1473d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -163,7 +163,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rc77abae3d94d447a"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R717c52cf45074037"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -193,7 +193,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R283d616b36de42bb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R40fb390dac5a4a43"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -223,7 +223,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R90239f6ec1834b40"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R538c28c0622942d8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -258,7 +258,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7a928429b2d7419f"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re111e16d38944ac6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -288,7 +288,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R6d728e7d941b4fc2"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R45df9479a0654076"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -318,7 +318,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0d14bbaf972d48eb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf1c28565a78e401c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -348,7 +348,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R51504d9ef13f490b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R737a27f590aa4ccd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -378,7 +378,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R82444285efde42be"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re8c174b36f404144"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -408,7 +408,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7373fc06cdef414e"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R10361a3266f7462a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -443,7 +443,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4433d205959c40a8"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ree0ca551c3c5495c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -473,7 +473,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R708d9ec8abad4dce"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0303558372e24f84"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -503,7 +503,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rca21c261e1254841"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra3ed50077930489a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -533,7 +533,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R77a2b4fa127d4910"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rca0ea2c86cca4b70"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -563,7 +563,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3f98bb55acd14c9f"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R26ab3490e61247b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -593,7 +593,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R56368cf8750b497b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R578951caa6484e88"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -628,7 +628,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R8cb54e6bc6904227"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R67e5822c0177456f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -658,7 +658,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra45055245f664c4f"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rc718859038ea4171"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -688,7 +688,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rde2b9dfbe67f4fcc"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3dc7c6ccf5724930"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -718,7 +718,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3dab901d5542481f"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rb3c3e485e8d64ca0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -753,7 +753,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Red051e1ce7e34d9a"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R60c2569b723a413b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -783,7 +783,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R62cf90c0b1654aa4"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R89282241cbf74627"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -813,7 +813,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rfd32c13ce85245a6"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rb7b42e93ccbe4bb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -843,7 +843,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R502d75bf63f34abb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4da80e1187074247"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -873,7 +873,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R6367229ff2e54b79"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R79744533e6f0467c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -903,7 +903,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R719c4398bc3c49f0"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rc94c8657112140c2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1134,8 +1134,6 @@
                 <a:solidFill>
                   <a:srgbClr val="F5F1E0"/>
                 </a:solidFill>
-                <a:latin typeface="Helvetica Neue"/>
-                <a:ea typeface="Helvetica Neue"/>
                 <a:effectLst>
                   <a:outerShdw blurRad="101600" dist="50800" dir="2700000" algn="tl" rotWithShape="0">
                     <a:srgbClr val="000000">
@@ -1143,6 +1141,8 @@
                     </a:srgbClr>
                   </a:outerShdw>
                 </a:effectLst>
+                <a:latin typeface="Helvetica Neue"/>
+                <a:ea typeface="Helvetica Neue"/>
               </a:rPr>
               <a:t>The Shape of Data · 200-sample bell curve</a:t>
             </a:r>
@@ -1152,7 +1152,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{E4B65545-8E62-44CA-A0D6-B93106F1CB38}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{729F077A-7707-4C0A-8E82-DC4BBD7422BF}">
           <cx:tx>
             <cx:txData>
               <cx:f>0-Hero!$B$1</cx:f>
@@ -1537,7 +1537,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{CBAA6141-6033-4886-9963-25DA70B731DE}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{7C9B4EFC-7410-49EF-B0DF-F3827E00B3AF}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -1572,7 +1572,7 @@
                     <a:latin typeface="Helvetica Neue"/>
                     <a:ea typeface="Helvetica Neue"/>
                   </a:rPr>
-                  <a:t>Monthly income ()</a:t>
+                  <a:t>Monthly income ($k)</a:t>
                 </a:r>
               </a:p>
             </cx:rich>
@@ -1854,7 +1854,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{2DD04932-2FCB-4A5E-ACAC-BDED8301773D}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{8726F31E-06E1-49D1-A202-ADA9B3522F9D}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -2191,7 +2191,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{D42E9717-B7A3-4871-86AF-34610FBA7963}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{030C633B-CE90-445A-9F41-0E9610F85407}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -2568,7 +2568,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{D0DBC94B-5164-4524-A3BC-1339437B2237}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{E1EE4671-82BE-4A97-B2F5-E5CD0B3B0E25}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -2934,8 +2934,6 @@
                 <a:solidFill>
                   <a:srgbClr val="F5F1E0"/>
                 </a:solidFill>
-                <a:latin typeface="Georgia"/>
-                <a:ea typeface="Georgia"/>
                 <a:effectLst>
                   <a:outerShdw blurRad="76200" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
                     <a:srgbClr val="000000">
@@ -2943,6 +2941,8 @@
                     </a:srgbClr>
                   </a:outerShdw>
                 </a:effectLst>
+                <a:latin typeface="Georgia"/>
+                <a:ea typeface="Georgia"/>
               </a:rPr>
               <a:t>Midnight Academia</a:t>
             </a:r>
@@ -2952,7 +2952,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{1A4063E4-8937-4B9B-B9A9-F47933E50238}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{BE9B8B96-9938-468D-ABBF-BA6DBEB42244}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -3336,7 +3336,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{14E4AC43-E7BB-4844-BE7C-DBC24211952F}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{5DEF2D98-A33E-41C5-8764-5163557350AF}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -3713,7 +3713,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{AAE69205-B2D1-4BA5-A568-E996D4D2FBE0}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{0B2B166B-299F-42DD-AD24-2C622C24DB0B}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -4090,7 +4090,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{C0D98DB5-D8EA-43DC-8801-858BBA8969BC}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{A8CDFD13-F626-40CE-8731-96CBE911C081}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -4456,8 +4456,6 @@
                 <a:solidFill>
                   <a:srgbClr val="00F0C8"/>
                 </a:solidFill>
-                <a:latin typeface="Courier New"/>
-                <a:ea typeface="Courier New"/>
                 <a:effectLst>
                   <a:outerShdw blurRad="76200" dist="0" dir="2700000" algn="tl" rotWithShape="0">
                     <a:srgbClr val="00F0C8">
@@ -4465,6 +4463,8 @@
                     </a:srgbClr>
                   </a:outerShdw>
                 </a:effectLst>
+                <a:latin typeface="Courier New"/>
+                <a:ea typeface="Courier New"/>
               </a:rPr>
               <a:t>Neon Terminal</a:t>
             </a:r>
@@ -4474,7 +4474,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{64ACDF9C-86BF-42CA-BD4A-95F28F36E1C1}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{B9BB2C76-5823-4C3C-954E-5782885A6533}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -4858,7 +4858,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{2AA6248E-CD0A-48FC-B4BD-632357F913F1}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{83E1473B-5221-4EFF-8F77-869E17B96CC4}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Theme Gallery!$B$1</cx:f>
@@ -5235,7 +5235,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{1B305BA3-BECC-4414-AE51-5EAAB561804F}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{3111DE53-7936-4486-8A19-0ABAD1D0F966}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -5610,7 +5610,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{1C2E4066-5490-4EF4-879D-75E200D6F4C9}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{EA341048-648D-472C-B9DF-615D6D40F273}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Typography!$B$1</cx:f>
@@ -5973,7 +5973,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{612F5C2B-857B-4619-9181-A7B5FB7747B5}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{6A93830B-2033-4770-A086-8378260F9710}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Typography!$B$1</cx:f>
@@ -6336,7 +6336,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{9FE62026-B118-40DE-B3B1-F6D566ADC450}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{88E26985-0546-4FDB-AED1-3F516A9D0DFE}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Typography!$B$1</cx:f>
@@ -6699,7 +6699,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{2C963140-25D7-4B5C-A929-64C4F710BCF7}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{20D9414A-0EE3-4004-9CC3-96F896902597}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Typography!$B$1</cx:f>
@@ -7112,7 +7112,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{13F03EC8-EC05-4198-A997-E7C2CFBE2A28}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{A979A9D4-2A79-4566-B093-1DCE998DE249}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -7536,7 +7536,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{DEC3BAF6-A6D7-437C-B6DB-9223A8DA7498}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{1FE19257-BD25-469E-847B-43CA726690FD}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -7893,7 +7893,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{9C0E743B-57D2-44A1-BA41-E6CD8B10ABBD}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{B7E2252A-E2C7-45E2-8212-16D5B6466A46}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -8250,7 +8250,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{067ECD80-2660-4ECB-8497-777E1C89B152}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{F8150D8B-5024-445E-8B81-C00088F15C61}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -8627,7 +8627,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{3F753698-6AD6-4B53-A15F-A0DF67FEE1AB}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{B7E92805-B122-4CBA-ACBD-DAF2F18A9E56}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -9024,7 +9024,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{1DEC5A3C-A71E-43E7-A997-17C8FAE6F7BE}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{2D30BB21-510A-47FE-9E53-4D07ADF5CAE7}">
           <cx:tx>
             <cx:txData>
               <cx:f>5-ML Dashboard!$B$1</cx:f>
@@ -9036,6 +9036,10 @@
               <a:srgbClr val="EC4899"/>
             </a:solidFill>
           </cx:spPr>
+          <cx:dataLabels>
+            <cx:numFmt formatCode="0" sourceLinked="0"/>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:binning intervalClosed="r" overflow="120">
@@ -9401,7 +9405,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{3A120FBC-1C3B-4BB1-B0D0-944A61B09A20}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{4C96CAA1-6CA6-4AEA-91DE-6653EB20A0EF}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -9778,7 +9782,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{7CC7F76C-81E4-4A37-B5F0-3D6756B5E5F3}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{E86CD489-5DA3-484C-A4CF-4AC2FE0BD2CB}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -10155,7 +10159,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{69A93BF1-CB7B-4660-99A8-25011DD28B85}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{89893EF8-B17C-4208-9B64-E674C9CE16F0}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -10532,7 +10536,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{3A80C3C1-41D4-42C9-AC71-6696DB0E8177}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{270172AD-8436-461E-96C8-DF13F8B2E157}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -10909,7 +10913,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{4D7B29CC-2C06-484A-ACF2-9986FD3C9022}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{8B88DE4F-D027-402F-B146-9818878A8D42}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Binning Lab!$B$1</cx:f>
@@ -11286,7 +11290,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{65769BA8-D1D9-4BAB-AB56-3851A4C803D8}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{0B046B23-547B-4A24-A39D-621A4F3AC388}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -11623,7 +11627,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{0147EBE4-1FB4-4FAB-9E09-E57970B051B9}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{D88A3AD6-C518-4AE4-B30C-62B52D0C5844}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Distribution Zoo!$B$1</cx:f>
@@ -27659,6 +27663,115 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
@@ -28668,7 +28781,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bef9993723a4c89"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb843b96f85b24e93"/>
 </x:worksheet>
 </file>
 
@@ -29681,7 +29794,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R846c01b1b3714fb4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57bad74a41c04517"/>
 </x:worksheet>
 </file>
 
@@ -30694,7 +30807,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569f1c6b4c364c59"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8913ddbb35e041a7"/>
 </x:worksheet>
 </file>
 
@@ -31707,7 +31820,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc02e8b4270b4aa2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8787a36406f48ce"/>
 </x:worksheet>
 </file>
 
@@ -32720,7 +32833,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R469790386495490b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03a218940eb5406c"/>
 </x:worksheet>
 </file>
 
@@ -33983,6 +34096,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8db07a2c4e44d03"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf58071658c84982"/>
 </x:worksheet>
 </file>